--- a/data/dividends_info_20260615.xlsx
+++ b/data/dividends_info_20260615.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>68.81999969482422</v>
+        <v>68.44999694824219</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1307759378074637</v>
+        <v>0.1314828400475352</v>
       </c>
       <c r="J2" t="n">
         <v>273</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.05000305175781</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="I3" t="n">
-        <v>1.092896122790721</v>
+        <v>1.09717869650597</v>
       </c>
       <c r="J3" t="n">
         <v>252</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.880000114440918</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6756756669679118</v>
+        <v>0.6593406317012648</v>
       </c>
       <c r="J4" t="n">
         <v>182</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>68.87999725341797</v>
+        <v>68.44999694824219</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306620261160565</v>
+        <v>0.1314828400475352</v>
       </c>
       <c r="J6" t="n">
         <v>182</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.079999923706055</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.701923212708811</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>161</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.15500068664551</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="I8" t="n">
-        <v>1.218686488972891</v>
+        <v>1.220063308807857</v>
       </c>
       <c r="J8" t="n">
         <v>161</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.25</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J10" t="n">
         <v>126</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>105</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.15500068664551</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="I14" t="n">
-        <v>1.218686488972891</v>
+        <v>1.220063308807857</v>
       </c>
       <c r="J14" t="n">
         <v>98</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>68.87999725341797</v>
+        <v>68.44999694824219</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1306620261160565</v>
+        <v>0.1314828400475352</v>
       </c>
       <c r="J15" t="n">
         <v>98</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6.019999980926514</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I16" t="n">
-        <v>4.983388720108072</v>
+        <v>5.067567502259338</v>
       </c>
       <c r="J16" t="n">
         <v>91</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J18" t="n">
         <v>49</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.849999904632568</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I19" t="n">
-        <v>4.273504343171475</v>
+        <v>4.288164721639967</v>
       </c>
       <c r="J19" t="n">
         <v>42</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.289999961853027</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="I20" t="n">
-        <v>3.263403292421668</v>
+        <v>3.240740611965279</v>
       </c>
       <c r="J20" t="n">
         <v>35</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.76200008392334</v>
+        <v>9.798999786376953</v>
       </c>
       <c r="I21" t="n">
-        <v>2.663388626969835</v>
+        <v>2.653332030494221</v>
       </c>
       <c r="J21" t="n">
         <v>35</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.68000030517578</v>
+        <v>14.60000038146973</v>
       </c>
       <c r="I22" t="n">
-        <v>4.087193375523676</v>
+        <v>4.10958893372029</v>
       </c>
       <c r="J22" t="n">
         <v>35</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.721999883651733</v>
+        <v>3.716000080108643</v>
       </c>
       <c r="I23" t="n">
-        <v>5.910800829583942</v>
+        <v>5.920344328775364</v>
       </c>
       <c r="J23" t="n">
         <v>35</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.610000133514404</v>
+        <v>6.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.512859273526701</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="J25" t="n">
         <v>35</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.047781523309159</v>
       </c>
       <c r="J27" t="n">
         <v>28</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.720000028610229</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I29" t="n">
-        <v>5.514705824346692</v>
+        <v>5.395683508766814</v>
       </c>
       <c r="J29" t="n">
         <v>28</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.630000114440918</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="I31" t="n">
-        <v>1.511879012306518</v>
+        <v>1.492537295223098</v>
       </c>
       <c r="J31" t="n">
         <v>21</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>36.54999923706055</v>
+        <v>35.90000152587891</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4103967253928277</v>
+        <v>0.4178272802909795</v>
       </c>
       <c r="J32" t="n">
         <v>21</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.45999908447266</v>
+        <v>22.36000061035156</v>
       </c>
       <c r="I34" t="n">
-        <v>1.113089983039373</v>
+        <v>1.118067948013662</v>
       </c>
       <c r="J34" t="n">
         <v>7</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>29.95000076293945</v>
+        <v>30.14999961853027</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6510851253175783</v>
+        <v>0.6467661773373704</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.865000009536743</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I36" t="n">
-        <v>1.769436988270957</v>
+        <v>1.764705877853063</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.449999809265137</v>
+        <v>5.494999885559082</v>
       </c>
       <c r="I37" t="n">
-        <v>5.321101103654953</v>
+        <v>5.277525132659658</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.79800009727478</v>
+        <v>3.796000003814697</v>
       </c>
       <c r="I38" t="n">
-        <v>4.212743441339207</v>
+        <v>4.214963114836984</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.70799994468689</v>
+        <v>2.721999883651733</v>
       </c>
       <c r="I39" t="n">
-        <v>5.118168494498456</v>
+        <v>5.091844449826332</v>
       </c>
       <c r="J39" t="n">
         <v>7</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>53.34999847412109</v>
+        <v>52</v>
       </c>
       <c r="I40" t="n">
-        <v>1.18088100847013</v>
+        <v>1.211538461538461</v>
       </c>
       <c r="J40" t="n">
         <v>7</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.34499979019165</v>
+        <v>6.394999980926514</v>
       </c>
       <c r="I41" t="n">
-        <v>2.206461853890326</v>
+        <v>2.189210327092396</v>
       </c>
       <c r="J41" t="n">
         <v>7</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.59000015258789</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I43" t="n">
-        <v>2.973067490253442</v>
+        <v>2.977233004253888</v>
       </c>
       <c r="J43" t="n">
         <v>7</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>68.87999725341797</v>
+        <v>68.44999694824219</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1306620261160565</v>
+        <v>0.1314828400475352</v>
       </c>
       <c r="J44" t="n">
         <v>7</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1.730000019073486</v>
+        <v>1.659999966621399</v>
       </c>
       <c r="I45" t="n">
-        <v>0.5780346757080136</v>
+        <v>0.6024096506672237</v>
       </c>
       <c r="J45" t="n">
         <v>7</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.343999862670898</v>
+        <v>6.374000072479248</v>
       </c>
       <c r="I46" t="n">
-        <v>2.857818472960536</v>
+        <v>2.844367711616311</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.15999984741211</v>
+        <v>10.14000034332275</v>
       </c>
       <c r="I48" t="n">
-        <v>2.726377993701995</v>
+        <v>2.731755331570635</v>
       </c>
       <c r="J48" t="n">
         <v>7</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.240000009536743</v>
+        <v>3.111999988555908</v>
       </c>
       <c r="I50" t="n">
-        <v>3.395061718401904</v>
+        <v>3.534704383178497</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.690000057220459</v>
+        <v>1.700000047683716</v>
       </c>
       <c r="I51" t="n">
-        <v>1.420118295112532</v>
+        <v>1.41176466628342</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.005000114440918</v>
+        <v>2.994999885559082</v>
       </c>
       <c r="I52" t="n">
-        <v>5.324459031834949</v>
+        <v>5.342237265900012</v>
       </c>
       <c r="J52" t="n">
         <v>-7</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8600000143051147</v>
+        <v>0.875</v>
       </c>
       <c r="I53" t="n">
-        <v>2.90697669583182</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="J53" t="n">
         <v>-7</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.64999961853027</v>
+        <v>27.85000038146973</v>
       </c>
       <c r="I54" t="n">
-        <v>4.014466601497197</v>
+        <v>3.985637288315981</v>
       </c>
       <c r="J54" t="n">
         <v>-11</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8799999952316284</v>
+        <v>0.9049999713897705</v>
       </c>
       <c r="I55" t="n">
-        <v>3.409090927563422</v>
+        <v>3.314917231868003</v>
       </c>
       <c r="J55" t="n">
         <v>-14</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.476500004529953</v>
+        <v>0.4760000109672546</v>
       </c>
       <c r="I56" t="n">
-        <v>4.826862493461783</v>
+        <v>4.831932661779336</v>
       </c>
       <c r="J56" t="n">
         <v>-14</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.70000076293945</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="I57" t="n">
-        <v>3.045685161234854</v>
+        <v>3.108808413048321</v>
       </c>
       <c r="J57" t="n">
         <v>-14</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.380000114440918</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I58" t="n">
-        <v>2.132196136032998</v>
+        <v>2.127659660812527</v>
       </c>
       <c r="J58" t="n">
         <v>-14</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.5</v>
+        <v>2.494999885559082</v>
       </c>
       <c r="I59" t="n">
-        <v>7.199999999999999</v>
+        <v>7.214429188627615</v>
       </c>
       <c r="J59" t="n">
         <v>-21</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8.25</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I60" t="n">
-        <v>3.636363636363636</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J60" t="n">
         <v>-21</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>16.70000076293945</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="I61" t="n">
-        <v>1.497005919633241</v>
+        <v>1.453488307620723</v>
       </c>
       <c r="J61" t="n">
         <v>-21</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.970000028610229</v>
+        <v>3.950000047683716</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7556675008514305</v>
+        <v>0.7594936617175999</v>
       </c>
       <c r="J62" t="n">
         <v>-21</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4.320000171661377</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="I63" t="n">
-        <v>3.472222084248513</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J63" t="n">
         <v>-21</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.64999961853027</v>
+        <v>12.69999980926514</v>
       </c>
       <c r="I64" t="n">
-        <v>4.584980375417487</v>
+        <v>4.566929202446662</v>
       </c>
       <c r="J64" t="n">
         <v>-21</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.266999959945679</v>
+        <v>2.275000095367432</v>
       </c>
       <c r="I65" t="n">
-        <v>4.587560733900146</v>
+        <v>4.571428379795436</v>
       </c>
       <c r="J65" t="n">
         <v>-28</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.60499954223633</v>
+        <v>10.46000003814697</v>
       </c>
       <c r="I66" t="n">
-        <v>2.734559288239689</v>
+        <v>2.772466529085927</v>
       </c>
       <c r="J66" t="n">
         <v>-28</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.079999923706055</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I67" t="n">
-        <v>3.701923212708811</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J67" t="n">
         <v>-28</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>42.13999938964844</v>
+        <v>41.88999938964844</v>
       </c>
       <c r="I68" t="n">
-        <v>3.891789330217363</v>
+        <v>3.915015573872902</v>
       </c>
       <c r="J68" t="n">
         <v>-28</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>37.22000122070312</v>
+        <v>37.29000091552734</v>
       </c>
       <c r="I69" t="n">
-        <v>5.373454955416624</v>
+        <v>5.363368063547597</v>
       </c>
       <c r="J69" t="n">
         <v>-28</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.296000003814697</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I70" t="n">
-        <v>3.033980579012828</v>
+        <v>3.030303074089731</v>
       </c>
       <c r="J70" t="n">
         <v>-28</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>36.88999938964844</v>
+        <v>35.4900016784668</v>
       </c>
       <c r="I71" t="n">
-        <v>0.4024396922100758</v>
+        <v>0.4183149985311965</v>
       </c>
       <c r="J71" t="n">
         <v>-28</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>21.54000091552734</v>
+        <v>21.65999984741211</v>
       </c>
       <c r="I72" t="n">
-        <v>4.271123309641125</v>
+        <v>4.247460787078074</v>
       </c>
       <c r="J72" t="n">
         <v>-28</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.42000007629395</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="I73" t="n">
-        <v>2.626970210120672</v>
+        <v>2.654867211825156</v>
       </c>
       <c r="J73" t="n">
         <v>-28</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>87.18000030517578</v>
+        <v>86.12000274658203</v>
       </c>
       <c r="I74" t="n">
-        <v>1.192934155034932</v>
+        <v>1.20761723970251</v>
       </c>
       <c r="J74" t="n">
         <v>-28</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>48.36999893188477</v>
+        <v>47.79000091552734</v>
       </c>
       <c r="I75" t="n">
-        <v>1.447178034851207</v>
+        <v>1.464741549675435</v>
       </c>
       <c r="J75" t="n">
         <v>-28</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>63.95000076293945</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="I76" t="n">
-        <v>3.440187605556609</v>
+        <v>3.448275903304479</v>
       </c>
       <c r="J76" t="n">
         <v>-28</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>10.83399963378906</v>
+        <v>10.78600025177002</v>
       </c>
       <c r="I77" t="n">
-        <v>7.937973316131868</v>
+        <v>7.973298534448587</v>
       </c>
       <c r="J77" t="n">
         <v>-28</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>13.43400001525879</v>
+        <v>13.47999954223633</v>
       </c>
       <c r="I78" t="n">
-        <v>4.168527611760705</v>
+        <v>4.154302811697991</v>
       </c>
       <c r="J78" t="n">
         <v>-28</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.450000047683716</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="I79" t="n">
-        <v>1.632653029448587</v>
+        <v>1.659750978233374</v>
       </c>
       <c r="J79" t="n">
         <v>-28</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>9.949999809265137</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I80" t="n">
-        <v>3.015075434681407</v>
+        <v>3.092783565969242</v>
       </c>
       <c r="J80" t="n">
         <v>-28</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>2.180000066757202</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I81" t="n">
-        <v>4.954128288658833</v>
+        <v>4.931506720464348</v>
       </c>
       <c r="J81" t="n">
         <v>-28</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>93.90000152587891</v>
+        <v>93.80000305175781</v>
       </c>
       <c r="I82" t="n">
-        <v>2.193823180537716</v>
+        <v>2.196161975456775</v>
       </c>
       <c r="J82" t="n">
         <v>-28</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>16.47999954223633</v>
+        <v>16.60000038146973</v>
       </c>
       <c r="I83" t="n">
-        <v>4.550971000198373</v>
+        <v>4.518072185330857</v>
       </c>
       <c r="J83" t="n">
         <v>-28</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>15.97000026702881</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="I84" t="n">
-        <v>1.878522197769596</v>
+        <v>1.879699243627516</v>
       </c>
       <c r="J84" t="n">
         <v>-28</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>38.56000137329102</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="I86" t="n">
-        <v>2.204356767966199</v>
+        <v>2.219321193034143</v>
       </c>
       <c r="J86" t="n">
         <v>-28</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>67.33999633789062</v>
+        <v>67.30000305175781</v>
       </c>
       <c r="I87" t="n">
-        <v>1.930502035487223</v>
+        <v>1.931649243760391</v>
       </c>
       <c r="J87" t="n">
         <v>-28</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>7.340000152587891</v>
+        <v>7.460000038146973</v>
       </c>
       <c r="I88" t="n">
-        <v>8.174386751047352</v>
+        <v>8.04289540123162</v>
       </c>
       <c r="J88" t="n">
         <v>-28</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.71999931335449</v>
+        <v>23.65999984741211</v>
       </c>
       <c r="I91" t="n">
-        <v>4.215851724063898</v>
+        <v>4.226542715338937</v>
       </c>
       <c r="J91" t="n">
         <v>-28</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.900000095367432</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I92" t="n">
-        <v>4.387755016643076</v>
+        <v>4.405737601599046</v>
       </c>
       <c r="J92" t="n">
         <v>-28</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>22.15500068664551</v>
+        <v>22.1299991607666</v>
       </c>
       <c r="I93" t="n">
-        <v>1.218686488972891</v>
+        <v>1.220063308807857</v>
       </c>
       <c r="J93" t="n">
         <v>-28</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>9.600000381469727</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="I94" t="n">
-        <v>2.083333250549108</v>
+        <v>2.061855710646161</v>
       </c>
       <c r="J94" t="n">
         <v>-28</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>9.210000038146973</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I95" t="n">
-        <v>2.605863181389165</v>
+        <v>2.591792592525459</v>
       </c>
       <c r="J95" t="n">
         <v>-28</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>22.34000015258789</v>
+        <v>22.22999954223633</v>
       </c>
       <c r="I96" t="n">
-        <v>3.536257809329001</v>
+        <v>3.553756258514643</v>
       </c>
       <c r="J96" t="n">
         <v>-28</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.360000133514404</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="I97" t="n">
-        <v>1.735074583645998</v>
+        <v>1.728624498545469</v>
       </c>
       <c r="J97" t="n">
         <v>-28</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.25</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J98" t="n">
         <v>-28</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>36.08000183105469</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9700664696162761</v>
+        <v>0.979294861675604</v>
       </c>
       <c r="J99" t="n">
         <v>-28</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.554999828338623</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="I100" t="n">
-        <v>8.45614057232536</v>
+        <v>8.360482510289398</v>
       </c>
       <c r="J100" t="n">
         <v>-28</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.269999980926514</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I101" t="n">
-        <v>2.643171828376432</v>
+        <v>2.620087379890132</v>
       </c>
       <c r="J101" t="n">
         <v>-28</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.55000019073486</v>
+        <v>13.39999961853027</v>
       </c>
       <c r="I102" t="n">
-        <v>1.476014739370667</v>
+        <v>1.492537355922225</v>
       </c>
       <c r="J102" t="n">
         <v>-28</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.300000190734863</v>
+        <v>7.255000114440918</v>
       </c>
       <c r="I103" t="n">
-        <v>1.410958867243966</v>
+        <v>1.419710522057481</v>
       </c>
       <c r="J103" t="n">
         <v>-28</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.916999816894531</v>
+        <v>5.885000228881836</v>
       </c>
       <c r="I104" t="n">
-        <v>3.211086798710082</v>
+        <v>3.228547028214822</v>
       </c>
       <c r="J104" t="n">
         <v>-28</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>10.48499965667725</v>
+        <v>10.52499961853027</v>
       </c>
       <c r="I105" t="n">
-        <v>4.1201718087314</v>
+        <v>4.104513212897628</v>
       </c>
       <c r="J105" t="n">
         <v>-28</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>27.36000061035156</v>
+        <v>26.65999984741211</v>
       </c>
       <c r="I106" t="n">
-        <v>1.608187098627211</v>
+        <v>1.650412612596886</v>
       </c>
       <c r="J106" t="n">
         <v>-28</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.880000114440918</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I108" t="n">
-        <v>6.831395235204775</v>
+        <v>6.911764512012579</v>
       </c>
       <c r="J108" t="n">
         <v>-28</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>53.68000030517578</v>
+        <v>53.84000015258789</v>
       </c>
       <c r="I109" t="n">
-        <v>2.60804767518791</v>
+        <v>2.600297169450708</v>
       </c>
       <c r="J109" t="n">
         <v>-28</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.450999975204468</v>
+        <v>3.493000030517578</v>
       </c>
       <c r="I110" t="n">
-        <v>8.693132487844348</v>
+        <v>8.588605707957788</v>
       </c>
       <c r="J110" t="n">
         <v>-28</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.85000038146973</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7570977735766636</v>
+        <v>0.75</v>
       </c>
       <c r="J111" t="n">
         <v>-28</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.349999904632568</v>
+        <v>3.319999933242798</v>
       </c>
       <c r="I112" t="n">
-        <v>5.074627010135566</v>
+        <v>5.120482030671402</v>
       </c>
       <c r="J112" t="n">
         <v>-28</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="I113" t="n">
-        <v>3.111111111111111</v>
+        <v>3.043478260869565</v>
       </c>
       <c r="J113" t="n">
         <v>-28</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.440000057220459</v>
+        <v>5.409999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>6.066176406781361</v>
+        <v>6.099815329160435</v>
       </c>
       <c r="J115" t="n">
         <v>-28</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.90000152587891</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I117" t="n">
-        <v>1.394891903174143</v>
+        <v>1.401776858066303</v>
       </c>
       <c r="J117" t="n">
         <v>-28</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>101.0999984741211</v>
+        <v>99.59999847412109</v>
       </c>
       <c r="I118" t="n">
-        <v>1.335311592853846</v>
+        <v>1.355421707512142</v>
       </c>
       <c r="J118" t="n">
         <v>-28</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.5</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I119" t="n">
-        <v>1.066666666666667</v>
+        <v>1.081081067148659</v>
       </c>
       <c r="J119" t="n">
         <v>-28</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.807000160217285</v>
+        <v>4.821000099182129</v>
       </c>
       <c r="I121" t="n">
-        <v>3.536509139461224</v>
+        <v>3.526239296880332</v>
       </c>
       <c r="J121" t="n">
         <v>-28</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>59.70000076293945</v>
+        <v>60.09999847412109</v>
       </c>
       <c r="I123" t="n">
-        <v>0.753768834588275</v>
+        <v>0.7487520988769557</v>
       </c>
       <c r="J123" t="n">
         <v>-28</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.699999809265137</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7017544094471985</v>
+        <v>0.704225373395827</v>
       </c>
       <c r="J124" t="n">
         <v>-28</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.29999923706055</v>
+        <v>37.61999893188477</v>
       </c>
       <c r="I125" t="n">
-        <v>2.74151441492453</v>
+        <v>2.791068659786894</v>
       </c>
       <c r="J125" t="n">
         <v>-28</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.549999952316284</v>
+        <v>1.5</v>
       </c>
       <c r="I126" t="n">
-        <v>3.225806550850609</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J126" t="n">
         <v>-28</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.06999969482422</v>
+        <v>17.32999992370605</v>
       </c>
       <c r="I127" t="n">
-        <v>2.226127749230244</v>
+        <v>2.192729380686207</v>
       </c>
       <c r="J127" t="n">
         <v>-28</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>26.84000015258789</v>
+        <v>26.61000061035156</v>
       </c>
       <c r="I128" t="n">
-        <v>2.235469435875352</v>
+        <v>2.254791380074579</v>
       </c>
       <c r="J128" t="n">
         <v>-28</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.40000152587891</v>
+        <v>37.65000152587891</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9358288388245591</v>
+        <v>0.9296148361625586</v>
       </c>
       <c r="J129" t="n">
         <v>-28</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>3.359999895095825</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="I130" t="n">
-        <v>0.505952396748964</v>
+        <v>0.5345911837459711</v>
       </c>
       <c r="J130" t="n">
         <v>-28</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>2.825000047683716</v>
+        <v>2.835000038146973</v>
       </c>
       <c r="I131" t="n">
-        <v>0.3539822949100208</v>
+        <v>0.352733681320733</v>
       </c>
       <c r="J131" t="n">
         <v>-28</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>24.54000091552734</v>
+        <v>24.27000045776367</v>
       </c>
       <c r="I132" t="n">
-        <v>4.563977009843287</v>
+        <v>4.614750634014619</v>
       </c>
       <c r="J132" t="n">
         <v>-28</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.350000023841858</v>
+        <v>1.340000033378601</v>
       </c>
       <c r="I133" t="n">
-        <v>7.407407276587888</v>
+        <v>7.462686381273111</v>
       </c>
       <c r="J133" t="n">
         <v>-28</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.407999992370605</v>
+        <v>2.460000038146973</v>
       </c>
       <c r="I135" t="n">
-        <v>3.833056490549792</v>
+        <v>3.752032462142813</v>
       </c>
       <c r="J135" t="n">
         <v>-28</v>
@@ -8694,129 +8694,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Abitare In S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CIRCLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rocket Sharing Company S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>